--- a/public/exports-60-250/29189900.xlsx
+++ b/public/exports-60-250/29189900.xlsx
@@ -5089,7 +5089,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056978</t>
+          <t xml:space="preserve">200056974</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -18064,7 +18064,7 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311914906</t>
+          <t xml:space="preserve">311914896</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
